--- a/whatsapp_urls.xlsx
+++ b/whatsapp_urls.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -477,36 +477,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kelly Chan Khe Lee</t>
+          <t>Lee Man Man</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://enamecard-one.vercel.app/?id=kelly</t>
+          <t>https://enamecard-one.vercel.app/?id=man</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lee Man Man</t>
+          <t>Lee Ah Seng (Shawn)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://enamecard-one.vercel.app/?id=man</t>
+          <t>https://enamecard-one.vercel.app/?id=shawn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lee Ah Seng (Shawn)</t>
+          <t>Stephent Lee</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://enamecard-one.vercel.app/?id=shawn</t>
+          <t>https://enamecard-one.vercel.app/?id=stephent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lee Aik Li (Lee)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://enamecard-one.vercel.app/?id=lee</t>
         </is>
       </c>
     </row>
@@ -517,6 +529,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
